--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2022/4TO_TRIMESTRE/FRACCIONES XXI-XXX/FRACC XXIX/LTAIPT_A63F29.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2022/4TO_TRIMESTRE/FRACCIONES XXI-XXX/FRACC XXIX/LTAIPT_A63F29.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="555" windowWidth="19815" windowHeight="7365"/>
+    <workbookView xWindow="330" yWindow="555" windowWidth="19815" windowHeight="8385"/>
   </bookViews>
   <sheets>
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="53">
   <si>
     <t>48984</t>
   </si>
@@ -67,6 +67,9 @@
     <t>436503</t>
   </si>
   <si>
+    <t>571937</t>
+  </si>
+  <si>
     <t>436513</t>
   </si>
   <si>
@@ -109,6 +112,9 @@
     <t>Denominación del área responsable de la elaboración y/o presentación del informe</t>
   </si>
   <si>
+    <t>ESTE CRITERIO APLICA A PARTIR DEL 01/04/2023 -&gt; Descripción de la temática que se aborda en el informe</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fundamento legal </t>
   </si>
   <si>
@@ -133,43 +139,40 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>2021</t>
-  </si>
-  <si>
-    <t>Informe Actividades</t>
-  </si>
-  <si>
-    <t>Dirección General</t>
-  </si>
-  <si>
-    <t>Ley que crea Colegio de Bachilleres del Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>Mensual</t>
+    <t>B44718D27A4E0E1A5511C43EE1CC70FC</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>01/01/2023</t>
+  </si>
+  <si>
+    <t>31/03/2023</t>
+  </si>
+  <si>
+    <t>Informe de actividades</t>
+  </si>
+  <si>
+    <t>Transaprencia y Archivo</t>
+  </si>
+  <si>
+    <t>Este dato no se requiere para este periodo, de conformidad con las últimas modificaciones a los Lineamientos Técnicos Generales, aprobadas por el Pleno del Consejo Nacional del Sistema Nacional de Transparencia.</t>
+  </si>
+  <si>
+    <t>Ley de General de Transparencia, Ley de Transparencia del Estado de Tlaxcala y Ley de Archivos del Estado de Tlaxcala</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>Unidad de Transparencia</t>
-  </si>
-  <si>
-    <t>A474962851F9A439</t>
-  </si>
-  <si>
-    <t>01/07/2021</t>
-  </si>
-  <si>
-    <t>30/09/2021</t>
-  </si>
-  <si>
-    <t>15/08/2021</t>
-  </si>
-  <si>
-    <t>10/10/2021</t>
-  </si>
-  <si>
-    <t>Durante el periodo del 01 de julio del 2021, al 30 de septiembre del 2021, El Colegio de Bachilleres del Estado de Tlaxcala, No genero reporte de actividades.</t>
+    <t>Área de transparencia y archivo</t>
+  </si>
+  <si>
+    <t>17/04/2023</t>
+  </si>
+  <si>
+    <t>Durante el periodo del 01 de enero del 2023, al 31 de marzo del 2023, el Colegio de Bachilleres del Estado de Tlaxcala, no ha generado informes, lo anterior por motivo de que estos son efectuados de forma anual mismo que generaliza todas las actividades efectuadas durante el ejercicio.</t>
   </si>
 </sst>
 </file>
@@ -562,31 +565,32 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35.140625" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="35.5703125" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="27.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="70.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="50.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="43.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="41.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="122.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="73.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="255" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="181.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="101.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="43.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="41.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="47.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="73.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="20" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="243.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -603,7 +607,7 @@
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
@@ -618,7 +622,7 @@
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>6</v>
       </c>
@@ -638,28 +642,31 @@
         <v>8</v>
       </c>
       <c r="H4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I4" t="s">
         <v>6</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>7</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>9</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>8</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>7</v>
       </c>
-      <c r="M4" t="s">
+      <c r="N4" t="s">
         <v>10</v>
       </c>
-      <c r="N4" t="s">
+      <c r="O4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>12</v>
       </c>
@@ -699,10 +706,13 @@
       <c r="N5" t="s">
         <v>24</v>
       </c>
+      <c r="O5" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -717,95 +727,102 @@
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
       <c r="N6" s="4"/>
+      <c r="O6" s="4"/>
     </row>
-    <row r="7" spans="1:14" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C8" s="2" t="s">
+      <c r="G8" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="H8" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>43</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>49</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>50</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>51</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A6:N6"/>
+    <mergeCell ref="A6:O6"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="G2:I2"/>
